--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:30:34+00:00</t>
+    <t>2026-06-16T13:53:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:53:28+00:00</t>
+    <t>2026-06-16T14:51:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:51:07+00:00</t>
+    <t>2026-06-17T12:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T12:15:06+00:00</t>
+    <t>2026-06-17T13:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:49:22+00:00</t>
+    <t>2026-06-17T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:07:59+00:00</t>
+    <t>2026-06-17T15:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:48:42+00:00</t>
+    <t>2026-06-18T10:03:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:03:06+00:00</t>
+    <t>2026-06-18T13:10:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:10:23+00:00</t>
+    <t>2026-06-18T14:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:01:22+00:00</t>
+    <t>2026-06-22T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
 </t>
   </si>
   <si>
-    <t>Number of Study Related Series</t>
+    <t>Nombre de séries</t>
   </si>
   <si>
     <t>Number of Series in the Study. This value given may be larger than the number of series elements this Resource contains due to resource availability, security, or other factors. This element should be present if any series elements are present.</t>
@@ -4384,7 +4384,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>245</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:03:44+00:00</t>
+    <t>2026-06-22T08:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:16:05+00:00</t>
+    <t>2026-06-22T09:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
+++ b/FixIssues/ig/StructureDefinition-fr-imaging-study-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:23:37+00:00</t>
+    <t>2026-06-22T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
